--- a/portfolio-lab/dist/examples/portfolio-m2-60-67.xlsx
+++ b/portfolio-lab/dist/examples/portfolio-m2-60-67.xlsx
@@ -418,7 +418,7 @@
     <col min="7" max="7" width="20.83203125" customWidth="1"/>
     <col min="8" max="8" width="20.83203125" customWidth="1"/>
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="21.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" customWidth="1"/>
   </cols>
@@ -452,7 +452,7 @@
         <v>ОФЗ / RGBITR</v>
       </c>
       <c r="J1" t="str">
-        <v>Нефть Brent</v>
+        <v>Индекс недвижимости</v>
       </c>
       <c r="K1" t="str">
         <v>Серебро</v>
@@ -490,7 +490,7 @@
         <v>100</v>
       </c>
       <c r="J2" s="1">
-        <v>4200</v>
+        <v>100</v>
       </c>
       <c r="K2" s="1">
         <v>38</v>
@@ -528,7 +528,7 @@
         <v>102.798978947</v>
       </c>
       <c r="J3" s="1">
-        <v>4559.901382674</v>
+        <v>103.566730321</v>
       </c>
       <c r="K3" s="1">
         <v>41.051547824</v>
@@ -566,7 +566,7 @@
         <v>107.209468146</v>
       </c>
       <c r="J4" s="1">
-        <v>5155.517098528</v>
+        <v>109.121956901</v>
       </c>
       <c r="K4" s="1">
         <v>45.876561813</v>
@@ -604,7 +604,7 @@
         <v>112.394440077</v>
       </c>
       <c r="J5" s="1">
-        <v>5856.695552199</v>
+        <v>115.210216076</v>
       </c>
       <c r="K5" s="1">
         <v>50.909230775</v>
@@ -642,7 +642,7 @@
         <v>117.21661311</v>
       </c>
       <c r="J6" s="1">
-        <v>6442.217481411</v>
+        <v>119.977718335</v>
       </c>
       <c r="K6" s="1">
         <v>53.974826232</v>
@@ -680,7 +680,7 @@
         <v>120.497481433</v>
       </c>
       <c r="J7" s="1">
-        <v>6668.015809736</v>
+        <v>121.826682291</v>
       </c>
       <c r="K7" s="1">
         <v>53.471613941</v>
@@ -718,7 +718,7 @@
         <v>121.415259536</v>
       </c>
       <c r="J8" s="1">
-        <v>6426.589124212</v>
+        <v>120.23176523</v>
       </c>
       <c r="K8" s="1">
         <v>49.804698987</v>
@@ -756,7 +756,7 @@
         <v>119.866408842</v>
       </c>
       <c r="J9" s="1">
-        <v>5854.42112511</v>
+        <v>116.117246089</v>
       </c>
       <c r="K9" s="1">
         <v>45.238117056</v>
@@ -794,7 +794,7 @@
         <v>116.549601313</v>
       </c>
       <c r="J10" s="1">
-        <v>5239.317483719</v>
+        <v>111.398749097</v>
       </c>
       <c r="K10" s="1">
         <v>42.135829399</v>
@@ -832,7 +832,7 @@
         <v>112.688330041</v>
       </c>
       <c r="J11" s="1">
-        <v>4826.775932209</v>
+        <v>108.045107267</v>
       </c>
       <c r="K11" s="1">
         <v>41.742993168</v>
@@ -870,7 +870,7 @@
         <v>109.570146181</v>
       </c>
       <c r="J12" s="1">
-        <v>4734.103286697</v>
+        <v>107.365622544</v>
       </c>
       <c r="K12" s="1">
         <v>44.256626321</v>
@@ -908,7 +908,7 @@
         <v>108.172399327</v>
       </c>
       <c r="J13" s="1">
-        <v>4984.355681921</v>
+        <v>109.785174625</v>
       </c>
       <c r="K13" s="1">
         <v>49.111588001</v>
@@ -946,7 +946,7 @@
         <v>108.996302518</v>
       </c>
       <c r="J14" s="1">
-        <v>5544.604667772</v>
+        <v>114.873890434</v>
       </c>
       <c r="K14" s="1">
         <v>54.883942802</v>
@@ -984,7 +984,7 @@
         <v>112.047086078</v>
       </c>
       <c r="J15" s="1">
-        <v>6313.799047324</v>
+        <v>121.408188281</v>
       </c>
       <c r="K15" s="1">
         <v>59.291336913</v>
@@ -1022,7 +1022,7 @@
         <v>116.854356229</v>
       </c>
       <c r="J16" s="1">
-        <v>7088.459831094</v>
+        <v>127.53545284</v>
       </c>
       <c r="K16" s="1">
         <v>60.136293872</v>
@@ -1060,7 +1060,7 @@
         <v>122.50578392</v>
       </c>
       <c r="J17" s="1">
-        <v>7583.720610363</v>
+        <v>131.277141761</v>
       </c>
       <c r="K17" s="1">
         <v>57.02111231</v>
@@ -1098,7 +1098,7 @@
         <v>127.761774227</v>
       </c>
       <c r="J18" s="1">
-        <v>7573.195489809</v>
+        <v>131.386868212</v>
       </c>
       <c r="K18" s="1">
         <v>51.944315931</v>
@@ -1136,7 +1136,7 @@
         <v>131.337799389</v>
       </c>
       <c r="J19" s="1">
-        <v>7070.995183092</v>
+        <v>128.084568879</v>
       </c>
       <c r="K19" s="1">
         <v>47.726523092</v>
@@ -1174,7 +1174,7 @@
         <v>132.338143587</v>
       </c>
       <c r="J20" s="1">
-        <v>6347.324578905</v>
+        <v>123.019281345</v>
       </c>
       <c r="K20" s="1">
         <v>46.212875498</v>
@@ -1212,7 +1212,7 @@
         <v>130.649953599</v>
       </c>
       <c r="J21" s="1">
-        <v>5731.898270554</v>
+        <v>118.419298745</v>
       </c>
       <c r="K21" s="1">
         <v>47.960875731</v>
@@ -1250,7 +1250,7 @@
         <v>127.034756031</v>
       </c>
       <c r="J22" s="1">
-        <v>5433.674029261</v>
+        <v>116.119528402</v>
       </c>
       <c r="K22" s="1">
         <v>52.616856206</v>
@@ -1288,7 +1288,7 @@
         <v>122.826113115</v>
       </c>
       <c r="J23" s="1">
-        <v>5525.12799701</v>
+        <v>117.06280987</v>
       </c>
       <c r="K23" s="1">
         <v>58.94096296</v>
@@ -1326,7 +1326,7 @@
         <v>119.427408001</v>
       </c>
       <c r="J24" s="1">
-        <v>5998.580665005</v>
+        <v>121.238124605</v>
       </c>
       <c r="K24" s="1">
         <v>64.662876259</v>
@@ -1364,7 +1364,7 @@
         <v>117.903915612</v>
       </c>
       <c r="J25" s="1">
-        <v>6782.117109558</v>
+        <v>127.741228933</v>
       </c>
       <c r="K25" s="1">
         <v>67.108747059</v>
@@ -1402,7 +1402,7 @@
         <v>118.801939627</v>
       </c>
       <c r="J26" s="1">
-        <v>7704.522039386</v>
+        <v>134.868316196</v>
       </c>
       <c r="K26" s="1">
         <v>64.980391861</v>
@@ -1440,7 +1440,7 @@
         <v>122.127180905</v>
       </c>
       <c r="J27" s="1">
-        <v>8474.780040327</v>
+        <v>140.449288301</v>
       </c>
       <c r="K27" s="1">
         <v>59.704091143</v>
@@ -1478,7 +1478,7 @@
         <v>127.366927621</v>
       </c>
       <c r="J28" s="1">
-        <v>8771.819246401</v>
+        <v>142.613737461</v>
       </c>
       <c r="K28" s="1">
         <v>54.38841943</v>
@@ -1516,7 +1516,7 @@
         <v>133.526774844</v>
       </c>
       <c r="J29" s="1">
-        <v>8454.220832254</v>
+        <v>140.746682735</v>
       </c>
       <c r="K29" s="1">
         <v>51.570989381</v>
@@ -1554,7 +1554,7 @@
         <v>139.255609939</v>
       </c>
       <c r="J30" s="1">
-        <v>7701.530015389</v>
+        <v>135.930111016</v>
       </c>
       <c r="K30" s="1">
         <v>52.305924174</v>
@@ -1592,7 +1592,7 @@
         <v>143.153345143</v>
       </c>
       <c r="J31" s="1">
-        <v>6892.357074887</v>
+        <v>130.406505853</v>
       </c>
       <c r="K31" s="1">
         <v>56.50629336</v>
@@ -1630,7 +1630,7 @@
         <v>144.243683332</v>
       </c>
       <c r="J32" s="1">
-        <v>6349.655913892</v>
+        <v>126.480638494</v>
       </c>
       <c r="K32" s="1">
         <v>63.147788514</v>
@@ -1668,7 +1668,7 @@
         <v>142.403618665</v>
       </c>
       <c r="J33" s="1">
-        <v>6227.744430969</v>
+        <v>125.685214585</v>
       </c>
       <c r="K33" s="1">
         <v>70.075114859</v>
@@ -1706,7 +1706,7 @@
         <v>138.463186987</v>
       </c>
       <c r="J34" s="1">
-        <v>6556.953125057</v>
+        <v>128.517610237</v>
       </c>
       <c r="K34" s="1">
         <v>74.294820216</v>
@@ -1744,7 +1744,7 @@
         <v>133.875921822</v>
       </c>
       <c r="J35" s="1">
-        <v>7293.964400538</v>
+        <v>134.474603949</v>
       </c>
       <c r="K35" s="1">
         <v>73.602162743</v>
@@ -1782,7 +1782,7 @@
         <v>130.171458914</v>
       </c>
       <c r="J36" s="1">
-        <v>8305.844734254</v>
+        <v>142.123836614</v>
       </c>
       <c r="K36" s="1">
         <v>68.554758124</v>
@@ -1820,7 +1820,7 @@
         <v>128.510908541</v>
       </c>
       <c r="J37" s="1">
-        <v>9324.916159157</v>
+        <v>149.296584675</v>
       </c>
       <c r="K37" s="1">
         <v>62.268987381</v>
@@ -1858,7 +1858,7 @@
         <v>129.489721513</v>
       </c>
       <c r="J38" s="1">
-        <v>9976.435015672</v>
+        <v>153.676710862</v>
       </c>
       <c r="K38" s="1">
         <v>57.998776251</v>
@@ -1896,7 +1896,7 @@
         <v>133.114111556</v>
       </c>
       <c r="J39" s="1">
-        <v>9962.589149423</v>
+        <v>153.805159729</v>
       </c>
       <c r="K39" s="1">
         <v>57.458048301</v>
@@ -1934,7 +1934,7 @@
         <v>138.825241738</v>
       </c>
       <c r="J40" s="1">
-        <v>9301.941298293</v>
+        <v>149.93939534</v>
       </c>
       <c r="K40" s="1">
         <v>60.917993171</v>
@@ -1972,7 +1972,7 @@
         <v>145.539247452</v>
       </c>
       <c r="J41" s="1">
-        <v>8349.947794528</v>
+        <v>144.009827425</v>
       </c>
       <c r="K41" s="1">
         <v>67.600710475</v>
@@ -2010,7 +2010,7 @@
         <v>151.783465883</v>
       </c>
       <c r="J42" s="1">
-        <v>7540.350383488</v>
+        <v>138.624958539</v>
       </c>
       <c r="K42" s="1">
         <v>75.546193435</v>
@@ -2048,7 +2048,7 @@
         <v>156.031853137</v>
       </c>
       <c r="J43" s="1">
-        <v>7148.034406118</v>
+        <v>135.932782755</v>
       </c>
       <c r="K43" s="1">
         <v>81.61284665</v>
@@ -2086,7 +2086,7 @@
         <v>157.220281448</v>
       </c>
       <c r="J44" s="1">
-        <v>7268.342710321</v>
+        <v>137.037014547</v>
       </c>
       <c r="K44" s="1">
         <v>82.775905984</v>
@@ -2124,7 +2124,7 @@
         <v>155.214678997</v>
       </c>
       <c r="J45" s="1">
-        <v>7891.172851082</v>
+        <v>141.924755296</v>
       </c>
       <c r="K45" s="1">
         <v>78.487946758</v>
@@ -2162,7 +2162,7 @@
         <v>150.919754164</v>
       </c>
       <c r="J46" s="1">
-        <v>8921.92026691</v>
+        <v>149.537471952</v>
       </c>
       <c r="K46" s="1">
         <v>71.499880273</v>
@@ -2200,7 +2200,7 @@
         <v>145.919804748</v>
       </c>
       <c r="J47" s="1">
-        <v>10135.350100808</v>
+        <v>157.880640564</v>
       </c>
       <c r="K47" s="1">
         <v>65.694207841</v>
@@ -2238,7 +2238,7 @@
         <v>141.882077151</v>
       </c>
       <c r="J48" s="1">
-        <v>11148.629635551</v>
+        <v>164.413883327</v>
       </c>
       <c r="K48" s="1">
         <v>63.610714781</v>
@@ -2276,7 +2276,7 @@
         <v>140.072138642</v>
       </c>
       <c r="J49" s="1">
-        <v>11539.386691191</v>
+        <v>166.947648333</v>
       </c>
       <c r="K49" s="1">
         <v>66.016787614</v>
@@ -2314,7 +2314,7 @@
         <v>141.13900859</v>
       </c>
       <c r="J50" s="1">
-        <v>11121.583860285</v>
+        <v>164.762021609</v>
       </c>
       <c r="K50" s="1">
         <v>72.42561292</v>
@@ -2352,7 +2352,7 @@
         <v>145.089459726</v>
       </c>
       <c r="J51" s="1">
-        <v>10131.414073295</v>
+        <v>159.123607415</v>
       </c>
       <c r="K51" s="1">
         <v>81.130566825</v>
@@ -2390,7 +2390,7 @@
         <v>151.314380457</v>
       </c>
       <c r="J52" s="1">
-        <v>9066.941676154</v>
+        <v>152.657520005</v>
       </c>
       <c r="K52" s="1">
         <v>89.006618486</v>
@@ -2428,7 +2428,7 @@
         <v>158.632398436</v>
       </c>
       <c r="J53" s="1">
-        <v>8353.014681245</v>
+        <v>148.061789362</v>
       </c>
       <c r="K53" s="1">
         <v>92.373290397</v>
@@ -2466,7 +2466,7 @@
         <v>165.438365646</v>
       </c>
       <c r="J54" s="1">
-        <v>8192.639312803</v>
+        <v>147.130643785</v>
       </c>
       <c r="K54" s="1">
         <v>89.443669723</v>
@@ -2504,7 +2504,7 @@
         <v>170.068950671</v>
       </c>
       <c r="J55" s="1">
-        <v>8625.715544366</v>
+        <v>150.446325721</v>
       </c>
       <c r="K55" s="1">
         <v>82.180991162</v>
@@ -2542,7 +2542,7 @@
         <v>171.364293587</v>
       </c>
       <c r="J56" s="1">
-        <v>9595.258790145</v>
+        <v>157.419749945</v>
       </c>
       <c r="K56" s="1">
         <v>74.864119543</v>
@@ -2580,7 +2580,7 @@
         <v>169.178261072</v>
       </c>
       <c r="J57" s="1">
-        <v>10926.394114297</v>
+        <v>166.374156636</v>
       </c>
       <c r="K57" s="1">
         <v>70.986006845</v>
@@ -2618,7 +2618,7 @@
         <v>164.496951809</v>
       </c>
       <c r="J58" s="1">
-        <v>12266.989366842</v>
+        <v>174.770777061</v>
       </c>
       <c r="K58" s="1">
         <v>71.997623781</v>
@@ -2656,7 +2656,7 @@
         <v>159.047191817</v>
       </c>
       <c r="J59" s="1">
-        <v>13124.066765582</v>
+        <v>179.898275851</v>
       </c>
       <c r="K59" s="1">
         <v>77.779313048</v>
@@ -2694,7 +2694,7 @@
         <v>154.64621803</v>
       </c>
       <c r="J60" s="1">
-        <v>13105.852436235</v>
+        <v>180.048641704</v>
       </c>
       <c r="K60" s="1">
         <v>86.921143099</v>
@@ -2732,7 +2732,7 @@
         <v>152.673451978</v>
       </c>
       <c r="J61" s="1">
-        <v>12236.765784225</v>
+        <v>175.523269287</v>
       </c>
       <c r="K61" s="1">
         <v>96.456411692</v>
@@ -2770,7 +2770,7 @@
         <v>153.836300774</v>
       </c>
       <c r="J62" s="1">
-        <v>10984.411984077</v>
+        <v>168.581950473</v>
       </c>
       <c r="K62" s="1">
         <v>102.26471665</v>
@@ -2808,7 +2808,7 @@
         <v>158.142146445</v>
       </c>
       <c r="J63" s="1">
-        <v>9919.381193114</v>
+        <v>162.278271647</v>
       </c>
       <c r="K63" s="1">
         <v>101.311293248</v>
@@ -2846,7 +2846,7 @@
         <v>164.927079876</v>
       </c>
       <c r="J64" s="1">
-        <v>9403.286909723</v>
+        <v>159.126735028</v>
       </c>
       <c r="K64" s="1">
         <v>94.363683688</v>
@@ -2884,7 +2884,7 @@
         <v>172.903448891</v>
       </c>
       <c r="J65" s="1">
-        <v>9561.553285872</v>
+        <v>160.419379791</v>
       </c>
       <c r="K65" s="1">
         <v>85.711498219</v>
@@ -2922,7 +2922,7 @@
         <v>180.321701501</v>
       </c>
       <c r="J66" s="1">
-        <v>10380.8904878</v>
+        <v>166.141106451</v>
       </c>
       <c r="K66" s="1">
         <v>79.833673493</v>
@@ -2960,7 +2960,7 @@
         <v>185.368867963</v>
       </c>
       <c r="J67" s="1">
-        <v>11736.845584238</v>
+        <v>175.052766476</v>
       </c>
       <c r="K67" s="1">
         <v>79.089376779</v>
@@ -2998,7 +2998,7 @@
         <v>186.780743846</v>
       </c>
       <c r="J68" s="1">
-        <v>13333.120619399</v>
+        <v>184.819514085</v>
       </c>
       <c r="K68" s="1">
         <v>83.851892938</v>
@@ -3036,7 +3036,7 @@
         <v>184.398049233</v>
       </c>
       <c r="J69" s="1">
-        <v>14666.09660183</v>
+        <v>192.46751164</v>
       </c>
       <c r="K69" s="1">
         <v>93.05046411</v>
@@ -3074,7 +3074,7 @@
         <v>179.295595227</v>
       </c>
       <c r="J70" s="1">
-        <v>15180.140113293</v>
+        <v>195.433608151</v>
       </c>
       <c r="K70" s="1">
         <v>103.987196459</v>
@@ -3112,7 +3112,7 @@
         <v>173.35555834</v>
       </c>
       <c r="J71" s="1">
-        <v>14630.517704181</v>
+        <v>192.875052094</v>
       </c>
       <c r="K71" s="1">
         <v>112.337772855</v>
@@ -3150,7 +3150,7 @@
         <v>168.558659637</v>
       </c>
       <c r="J72" s="1">
-        <v>13327.942748969</v>
+        <v>186.274566007</v>
       </c>
       <c r="K72" s="1">
         <v>113.9386911</v>
@@ -3188,7 +3188,7 @@
         <v>166.408417584</v>
       </c>
       <c r="J73" s="1">
-        <v>11927.622214805</v>
+        <v>178.705182396</v>
       </c>
       <c r="K73" s="1">
         <v>108.036436623</v>
@@ -3226,7 +3226,7 @@
         <v>167.675879775</v>
       </c>
       <c r="J74" s="1">
-        <v>10988.446493996</v>
+        <v>173.325290972</v>
       </c>
       <c r="K74" s="1">
         <v>98.417560947</v>
@@ -3264,7 +3264,7 @@
         <v>172.369092348</v>
       </c>
       <c r="J75" s="1">
-        <v>10777.471627756</v>
+        <v>172.235265794</v>
       </c>
       <c r="K75" s="1">
         <v>90.42621721</v>
@@ -3302,7 +3302,7 @@
         <v>179.764418916</v>
       </c>
       <c r="J76" s="1">
-        <v>11347.186297244</v>
+        <v>176.116696236</v>
       </c>
       <c r="K76" s="1">
         <v>87.558347999</v>
@@ -3340,7 +3340,7 @@
         <v>188.458366217</v>
       </c>
       <c r="J77" s="1">
-        <v>12622.626899998</v>
+        <v>184.279982576</v>
       </c>
       <c r="K77" s="1">
         <v>90.870239134</v>
@@ -3378,7 +3378,7 @@
         <v>196.543987274</v>
       </c>
       <c r="J78" s="1">
-        <v>14373.744292208</v>
+        <v>194.762262656</v>
       </c>
       <c r="K78" s="1">
         <v>99.691805727</v>
@@ -3416,7 +3416,7 @@
         <v>202.045212099</v>
       </c>
       <c r="J79" s="1">
-        <v>16137.306283277</v>
+        <v>204.59158246</v>
       </c>
       <c r="K79" s="1">
         <v>111.673928329</v>
@@ -3454,7 +3454,7 @@
         <v>203.584104608</v>
       </c>
       <c r="J80" s="1">
-        <v>17264.79731456</v>
+        <v>210.59397662</v>
       </c>
       <c r="K80" s="1">
         <v>122.51509046</v>
@@ -3492,7 +3492,7 @@
         <v>200.98705558</v>
       </c>
       <c r="J81" s="1">
-        <v>17240.836242888</v>
+        <v>210.769999112</v>
       </c>
       <c r="K81" s="1">
         <v>127.149219031</v>
@@ -3530,7 +3530,7 @@
         <v>195.425569375</v>
       </c>
       <c r="J82" s="1">
-        <v>16097.546958876</v>
+        <v>205.472471004</v>
       </c>
       <c r="K82" s="1">
         <v>123.116679114</v>
@@ -3568,7 +3568,7 @@
         <v>188.951148801</v>
       </c>
       <c r="J83" s="1">
-        <v>14450.067186648</v>
+        <v>197.346768158</v>
       </c>
       <c r="K83" s="1">
         <v>113.119807691</v>
@@ -3606,7 +3606,7 @@
         <v>183.722706579</v>
       </c>
       <c r="J84" s="1">
-        <v>13049.012081689</v>
+        <v>189.967504599</v>
       </c>
       <c r="K84" s="1">
         <v>103.048341057</v>
@@ -3644,7 +3644,7 @@
         <v>181.379022245</v>
       </c>
       <c r="J85" s="1">
-        <v>12370.086611627</v>
+        <v>186.278227278</v>
       </c>
       <c r="K85" s="1">
         <v>97.710228722</v>
@@ -3682,7 +3682,7 @@
         <v>182.760509169</v>
       </c>
       <c r="J86" s="1">
-        <v>12578.287084447</v>
+        <v>187.79143356</v>
       </c>
       <c r="K86" s="1">
         <v>99.102690794</v>
@@ -3879,13 +3879,13 @@
         <v>Рублёвая масса М2</v>
       </c>
       <c r="B2" s="2">
-        <v>0.6066999962683716</v>
+        <v>0.6066999997943098</v>
       </c>
       <c r="C2" s="2">
-        <v>0.5382390778822271</v>
+        <v>0.6236920121348946</v>
       </c>
       <c r="D2" s="2">
-        <v>0.5838855631643681</v>
+        <v>0.6242210033496696</v>
       </c>
       <c r="E2" s="2">
         <v>0</v>
@@ -3905,13 +3905,13 @@
         <v>Золото</v>
       </c>
       <c r="B3" s="2">
-        <v>0.06292799962319016</v>
+        <v>0.06292800009154875</v>
       </c>
       <c r="C3" s="2">
-        <v>0.09700401821899995</v>
+        <v>0.10469477597694865</v>
       </c>
       <c r="D3" s="2">
-        <v>0.059615761397458465</v>
+        <v>0.06526981680299368</v>
       </c>
       <c r="E3" s="2">
         <v>0</v>
@@ -3931,13 +3931,13 @@
         <v>Доллар США</v>
       </c>
       <c r="B4" s="2">
-        <v>0.047196000605061496</v>
+        <v>0.04719600002604541</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>0.051088136178919705</v>
+        <v>0.04541660161281849</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
@@ -3957,13 +3957,13 @@
         <v>Евро</v>
       </c>
       <c r="B5" s="2">
-        <v>0.03146400073290321</v>
+        <v>0.031464000004747535</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>0.036399611884894156</v>
+        <v>0.02897969603042031</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -3983,13 +3983,13 @@
         <v>Юань</v>
       </c>
       <c r="B6" s="2">
-        <v>0.031464001433853604</v>
+        <v>0.03146399997871247</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>0.04138987131149425</v>
+        <v>0.02621252342737745</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -4009,13 +4009,13 @@
         <v>Индекс Мосбиржи</v>
       </c>
       <c r="B7" s="2">
-        <v>0.05112899970926641</v>
+        <v>0.0511290000766759</v>
       </c>
       <c r="C7" s="2">
-        <v>0.0750492091601122</v>
+        <v>0.08140520797190579</v>
       </c>
       <c r="D7" s="2">
-        <v>0.04852432861887103</v>
+        <v>0.052983748161204464</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -4035,13 +4035,13 @@
         <v>ОФЗ / RGBITR</v>
       </c>
       <c r="B8" s="2">
-        <v>0.039330002679995486</v>
+        <v>0.03932999991747358</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
       </c>
       <c r="D8" s="2">
-        <v>0.05819829108956619</v>
+        <v>0.029182960906520998</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -4058,25 +4058,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Нефть Brent</v>
+        <v>Индекс недвижимости</v>
       </c>
       <c r="B9" s="2">
-        <v>0.0393299996133347</v>
+        <v>0.039329999967786695</v>
       </c>
       <c r="C9" s="2">
-        <v>0.10939123183485917</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2">
-        <v>0.03613968740870792</v>
+        <v>0.03338764964716278</v>
       </c>
       <c r="E9" s="2">
-        <v>0.6049895819753921</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>0.15246092857094923</v>
+        <v>0.0483937485712914</v>
       </c>
       <c r="G9" s="2">
-        <v>0.2999999999997215</v>
+        <v>0.11999999999986001</v>
       </c>
       <c r="H9" s="2">
         <v>0.039330000000000004</v>
@@ -4087,16 +4087,16 @@
         <v>Серебро</v>
       </c>
       <c r="B10" s="2">
-        <v>0.03932999973496067</v>
+        <v>0.039330000057007646</v>
       </c>
       <c r="C10" s="2">
-        <v>0.06961672703788915</v>
+        <v>0.07416746968474634</v>
       </c>
       <c r="D10" s="2">
-        <v>0.037053357378830455</v>
+        <v>0.040908139194808964</v>
       </c>
       <c r="E10" s="2">
-        <v>0.04898435345596692</v>
+        <v>0.19344861283941767</v>
       </c>
       <c r="F10" s="2">
         <v>0.12162620857190501</v>
@@ -4113,16 +4113,16 @@
         <v>Индекс S&amp;P 500</v>
       </c>
       <c r="B11" s="2">
-        <v>0.05112899959906274</v>
+        <v>0.05112900008569232</v>
       </c>
       <c r="C11" s="2">
-        <v>0.11069973586591236</v>
+        <v>0.11604053423150461</v>
       </c>
       <c r="D11" s="2">
-        <v>0.04770539156688964</v>
+        <v>0.05343786086702327</v>
       </c>
       <c r="E11" s="2">
-        <v>0.346026064568641</v>
+        <v>0.8065513871605823</v>
       </c>
       <c r="F11" s="2">
         <v>0.13164749257087444</v>
@@ -4139,13 +4139,13 @@
         <v>Сумма весов</v>
       </c>
       <c r="B12" s="2">
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -4156,16 +4156,16 @@
         <v>Ожидаемая реальная доходность</v>
       </c>
       <c r="B13" s="2">
-        <v>0.10249316118881416</v>
+        <v>0.09840019936228528</v>
       </c>
       <c r="C13" s="2">
-        <v>0.11620394956418739</v>
+        <v>0.11138594129258766</v>
       </c>
       <c r="D13" s="2">
-        <v>0.1</v>
+        <v>0.10000000000000003</v>
       </c>
       <c r="E13" s="2">
-        <v>0.14374851839854313</v>
+        <v>0.12970888908240394</v>
       </c>
     </row>
     <row r="14">
@@ -4173,16 +4173,16 @@
         <v>Ожидаемая волатильность</v>
       </c>
       <c r="B14" s="2">
-        <v>0.045957039649176204</v>
+        <v>0.044666628899157686</v>
       </c>
       <c r="C14" s="2">
-        <v>0.061663448576663914</v>
+        <v>0.057506607604680085</v>
       </c>
       <c r="D14" s="2">
-        <v>0.04450118317353439</v>
+        <v>0.04572444380406572</v>
       </c>
       <c r="E14" s="2">
-        <v>0.19999999999999968</v>
+        <v>0.19999999999999998</v>
       </c>
     </row>
     <row r="15">
@@ -4190,16 +4190,16 @@
         <v>Коэффициент Шарпа</v>
       </c>
       <c r="B15">
-        <v>1.608496395374375</v>
+        <v>1.5633320112180011</v>
       </c>
       <c r="C15">
-        <v>1.4211420706417364</v>
+        <v>1.4400869077662466</v>
       </c>
       <c r="D15">
-        <v>1.6050937601012547</v>
+        <v>1.5621528768079131</v>
       </c>
       <c r="E15">
-        <v>0.5758854491375316</v>
+        <v>0.5056873025568347</v>
       </c>
     </row>
     <row r="16">
@@ -4340,10 +4340,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Нефть Brent</v>
+        <v>Индекс недвижимости</v>
       </c>
       <c r="B9" t="str">
-        <v>₽ за баррель, условный уровень</v>
+        <v>Индекс рублёвых цен на жильё, январь 2019 = 100; без арендного дохода</v>
       </c>
       <c r="C9" t="str">
         <v>Синтетический генератор</v>
